--- a/exercise/Admin/Admin Kantor/Tes Excel Admin Kantor.xlsx
+++ b/exercise/Admin/Admin Kantor/Tes Excel Admin Kantor.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Kantor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Kantor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB50B0D-D578-4C41-B6F1-B7B4DADF3D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="1. Absolute" sheetId="2" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="3. F. Statistik" sheetId="4" r:id="rId3"/>
     <sheet name="4. IF" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -272,7 +271,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -468,7 +467,7 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -511,6 +510,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -520,19 +522,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -822,7 +824,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -838,18 +840,18 @@
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B2" s="15" t="s">
@@ -905,151 +907,451 @@
       <c r="B4" s="2">
         <v>1</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
+      <c r="C4" s="12">
+        <f>C$3*$B4</f>
+        <v>1</v>
+      </c>
+      <c r="D4" s="12">
+        <f t="shared" ref="D4:L13" si="0">D$3*$B4</f>
+        <v>2</v>
+      </c>
+      <c r="E4" s="12">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F4" s="12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H4" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="K4" s="12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="L4" s="12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>2</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
+      <c r="C5" s="12">
+        <f t="shared" ref="C5:C13" si="1">C$3*$B5</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E5" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F5" s="12">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="G5" s="12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="H5" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="K5" s="12">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="L5" s="12">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>3</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
+      <c r="C6" s="12">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="D6" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E6" s="12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="F6" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="G6" s="12">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="H6" s="12">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="K6" s="12">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="L6" s="12">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>4</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
+      <c r="C7" s="12">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="D7" s="12">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="E7" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="F7" s="12">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="G7" s="12">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="H7" s="12">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="I7" s="12">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="J7" s="12">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="K7" s="12">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="L7" s="12">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>5</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
+      <c r="C8" s="12">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="D8" s="12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E8" s="12">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F8" s="12">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="G8" s="12">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="H8" s="12">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="I8" s="12">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="J8" s="12">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="K8" s="12">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="L8" s="12">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>6</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
+      <c r="C9" s="12">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="D9" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="E9" s="12">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="F9" s="12">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="G9" s="12">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H9" s="12">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="I9" s="12">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="J9" s="12">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="K9" s="12">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="L9" s="12">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>7</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
+      <c r="C10" s="12">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="D10" s="12">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="E10" s="12">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="F10" s="12">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="G10" s="12">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="H10" s="12">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="I10" s="12">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="K10" s="12">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="L10" s="12">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>8</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
+      <c r="C11" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="D11" s="12">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="E11" s="12">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="F11" s="12">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="G11" s="12">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="H11" s="12">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="I11" s="12">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="J11" s="12">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="K11" s="12">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="L11" s="12">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>9</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
+      <c r="C12" s="12">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="D12" s="12">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="E12" s="12">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="F12" s="12">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="G12" s="12">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H12" s="12">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="I12" s="12">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="J12" s="12">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="K12" s="12">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="L12" s="12">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>10</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
+      <c r="C13" s="12">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="D13" s="12">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="E13" s="12">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="F13" s="12">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="G13" s="12">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="H13" s="12">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="I13" s="12">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="J13" s="12">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="K13" s="12">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="L13" s="12">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
@@ -1070,7 +1372,7 @@
     <mergeCell ref="C1:L1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C1" r:id="rId1" xr:uid="{1D8F91B2-4516-405D-81FD-321D8B0C5FF1}"/>
+    <hyperlink ref="C1" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -1078,7 +1380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -1132,11 +1434,26 @@
       <c r="C4" s="2">
         <v>4</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
+      <c r="D4" s="9">
+        <f>B4*C4</f>
+        <v>40</v>
+      </c>
+      <c r="E4" s="9">
+        <f>C4/B4</f>
+        <v>0.4</v>
+      </c>
+      <c r="F4" s="9">
+        <f>POWER(B4,3)</f>
+        <v>1000</v>
+      </c>
+      <c r="G4" s="9">
+        <f>POWER(C4,2)</f>
+        <v>16</v>
+      </c>
+      <c r="H4" s="9">
+        <f>POWER((B4+C4),2)</f>
+        <v>196</v>
+      </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
@@ -1145,11 +1462,26 @@
       <c r="C5" s="2">
         <v>9</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="D5" s="9">
+        <f t="shared" ref="D5:D13" si="0">B5*C5</f>
+        <v>81</v>
+      </c>
+      <c r="E5" s="9">
+        <f t="shared" ref="E5:E13" si="1">C5/B5</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="9">
+        <f t="shared" ref="F5:F13" si="2">POWER(B5,3)</f>
+        <v>729</v>
+      </c>
+      <c r="G5" s="9">
+        <f t="shared" ref="G5:G13" si="3">POWER(C5,2)</f>
+        <v>81</v>
+      </c>
+      <c r="H5" s="9">
+        <f t="shared" ref="H5:H13" si="4">POWER((B5+C5),2)</f>
+        <v>324</v>
+      </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
@@ -1158,11 +1490,26 @@
       <c r="C6" s="2">
         <v>16</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="D6" s="9">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+      <c r="E6" s="9">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F6" s="9">
+        <f t="shared" si="2"/>
+        <v>512</v>
+      </c>
+      <c r="G6" s="9">
+        <f t="shared" si="3"/>
+        <v>256</v>
+      </c>
+      <c r="H6" s="9">
+        <f t="shared" si="4"/>
+        <v>576</v>
+      </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
@@ -1171,11 +1518,26 @@
       <c r="C7" s="2">
         <v>25</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="D7" s="9">
+        <f t="shared" si="0"/>
+        <v>175</v>
+      </c>
+      <c r="E7" s="9">
+        <f t="shared" si="1"/>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="F7" s="9">
+        <f t="shared" si="2"/>
+        <v>343</v>
+      </c>
+      <c r="G7" s="9">
+        <f t="shared" si="3"/>
+        <v>625</v>
+      </c>
+      <c r="H7" s="9">
+        <f t="shared" si="4"/>
+        <v>1024</v>
+      </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
@@ -1184,11 +1546,26 @@
       <c r="C8" s="2">
         <v>36</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="D8" s="9">
+        <f t="shared" si="0"/>
+        <v>216</v>
+      </c>
+      <c r="E8" s="9">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="F8" s="9">
+        <f t="shared" si="2"/>
+        <v>216</v>
+      </c>
+      <c r="G8" s="9">
+        <f t="shared" si="3"/>
+        <v>1296</v>
+      </c>
+      <c r="H8" s="9">
+        <f t="shared" si="4"/>
+        <v>1764</v>
+      </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
@@ -1197,11 +1574,26 @@
       <c r="C9" s="2">
         <v>49</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="D9" s="9">
+        <f t="shared" si="0"/>
+        <v>245</v>
+      </c>
+      <c r="E9" s="9">
+        <f t="shared" si="1"/>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="F9" s="9">
+        <f t="shared" si="2"/>
+        <v>125</v>
+      </c>
+      <c r="G9" s="9">
+        <f t="shared" si="3"/>
+        <v>2401</v>
+      </c>
+      <c r="H9" s="9">
+        <f t="shared" si="4"/>
+        <v>2916</v>
+      </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
@@ -1210,11 +1602,26 @@
       <c r="C10" s="2">
         <v>64</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="D10" s="9">
+        <f t="shared" si="0"/>
+        <v>256</v>
+      </c>
+      <c r="E10" s="9">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="F10" s="9">
+        <f t="shared" si="2"/>
+        <v>64</v>
+      </c>
+      <c r="G10" s="9">
+        <f t="shared" si="3"/>
+        <v>4096</v>
+      </c>
+      <c r="H10" s="9">
+        <f t="shared" si="4"/>
+        <v>4624</v>
+      </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
@@ -1223,11 +1630,26 @@
       <c r="C11" s="2">
         <v>81</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="D11" s="9">
+        <f t="shared" si="0"/>
+        <v>243</v>
+      </c>
+      <c r="E11" s="9">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="F11" s="9">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="G11" s="9">
+        <f t="shared" si="3"/>
+        <v>6561</v>
+      </c>
+      <c r="H11" s="9">
+        <f t="shared" si="4"/>
+        <v>7056</v>
+      </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
@@ -1236,11 +1658,26 @@
       <c r="C12" s="2">
         <v>100</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="D12" s="9">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E12" s="9">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="F12" s="9">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="G12" s="9">
+        <f t="shared" si="3"/>
+        <v>10000</v>
+      </c>
+      <c r="H12" s="9">
+        <f t="shared" si="4"/>
+        <v>10404</v>
+      </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
@@ -1249,11 +1686,26 @@
       <c r="C13" s="2">
         <v>121</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
+      <c r="D13" s="9">
+        <f t="shared" si="0"/>
+        <v>121</v>
+      </c>
+      <c r="E13" s="9">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+      <c r="F13" s="9">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G13" s="9">
+        <f t="shared" si="3"/>
+        <v>14641</v>
+      </c>
+      <c r="H13" s="9">
+        <f t="shared" si="4"/>
+        <v>14884</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1264,7 +1716,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -1320,7 +1772,10 @@
       <c r="E4" s="8">
         <v>2000</v>
       </c>
-      <c r="F4" s="13"/>
+      <c r="F4" s="13">
+        <f>E4*E4</f>
+        <v>4000000</v>
+      </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
@@ -1335,7 +1790,10 @@
       <c r="E5" s="8">
         <v>3000</v>
       </c>
-      <c r="F5" s="13"/>
+      <c r="F5" s="13">
+        <f t="shared" ref="F5:F8" si="0">E5*E5</f>
+        <v>9000000</v>
+      </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
@@ -1350,7 +1808,10 @@
       <c r="E6" s="8">
         <v>4000</v>
       </c>
-      <c r="F6" s="13"/>
+      <c r="F6" s="13">
+        <f t="shared" si="0"/>
+        <v>16000000</v>
+      </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
@@ -1365,7 +1826,10 @@
       <c r="E7" s="8">
         <v>5000</v>
       </c>
-      <c r="F7" s="13"/>
+      <c r="F7" s="13">
+        <f t="shared" si="0"/>
+        <v>25000000</v>
+      </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
@@ -1380,52 +1844,70 @@
       <c r="E8" s="8">
         <v>6000</v>
       </c>
-      <c r="F8" s="13"/>
+      <c r="F8" s="13">
+        <f t="shared" si="0"/>
+        <v>36000000</v>
+      </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="13"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="13">
+        <f>SUM(F4:F8)</f>
+        <v>90000000</v>
+      </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="13"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="13">
+        <f>MAX(F4:F8)</f>
+        <v>36000000</v>
+      </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="13"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="13">
+        <f>MIN(F4:F8)</f>
+        <v>4000000</v>
+      </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="13"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="13">
+        <f>AVERAGE(F4:F8)</f>
+        <v>18000000</v>
+      </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="12">
+        <f>SUM(D4:D8)</f>
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1441,7 +1923,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -1459,11 +1941,11 @@
       <c r="B1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
@@ -1501,13 +1983,34 @@
       <c r="C3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
+      <c r="D3" s="12" t="str">
+        <f>IF(LEFT(B3,3)="MAN","Manager",IF(LEFT(B3,3)="SKT","Sekretaris",IF(LEFT(B3,3)="KEU","Keuangan")))</f>
+        <v>Manager</v>
+      </c>
+      <c r="E3" s="12" t="str">
+        <f>MID(B3,5,1)</f>
+        <v>1</v>
+      </c>
+      <c r="F3" s="12" t="str">
+        <f>IF(RIGHT(B3,1)="A","Menikah","Belum")</f>
+        <v>Menikah</v>
+      </c>
+      <c r="G3" s="14">
+        <f>IF(E3="1",5000000,IF(E3="2",4000000,IF(E3="3",3000000,IF(E3="4",2000000))))</f>
+        <v>5000000</v>
+      </c>
+      <c r="H3" s="14">
+        <f>IF(AND(OR(E3="3",E3="4"),F3="Menikah"),G3*0.3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="14">
+        <f>IF(OR(D3="Sekretaris",D3="Keuangan"),500000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="14">
+        <f>G3+H3+I3</f>
+        <v>5000000</v>
+      </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
@@ -1516,13 +2019,34 @@
       <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
+      <c r="D4" s="12" t="str">
+        <f t="shared" ref="D4:D10" si="0">IF(LEFT(B4,3)="MAN","Manager",IF(LEFT(B4,3)="SKT","Sekretaris",IF(LEFT(B4,3)="KEU","Keuangan")))</f>
+        <v>Sekretaris</v>
+      </c>
+      <c r="E4" s="12" t="str">
+        <f t="shared" ref="E4:E10" si="1">MID(B4,5,1)</f>
+        <v>2</v>
+      </c>
+      <c r="F4" s="12" t="str">
+        <f t="shared" ref="F4:F10" si="2">IF(RIGHT(B4,1)="A","Menikah","Belum")</f>
+        <v>Belum</v>
+      </c>
+      <c r="G4" s="14">
+        <f t="shared" ref="G4:G10" si="3">IF(E4="1",5000000,IF(E4="2",4000000,IF(E4="3",3000000,IF(E4="4",2000000))))</f>
+        <v>4000000</v>
+      </c>
+      <c r="H4" s="14">
+        <f t="shared" ref="H4:H10" si="4">IF(AND(OR(E4="3",E4="4"),F4="Menikah"),G4*0.3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="14">
+        <f t="shared" ref="I4:I10" si="5">IF(OR(D4="Sekretaris",D4="Keuangan"),500000,0)</f>
+        <v>500000</v>
+      </c>
+      <c r="J4" s="14">
+        <f t="shared" ref="J4:J10" si="6">G4+H4+I4</f>
+        <v>4500000</v>
+      </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
@@ -1531,13 +2055,34 @@
       <c r="C5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
+      <c r="D5" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Manager</v>
+      </c>
+      <c r="E5" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="F5" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Belum</v>
+      </c>
+      <c r="G5" s="14">
+        <f t="shared" si="3"/>
+        <v>3000000</v>
+      </c>
+      <c r="H5" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="14">
+        <f t="shared" si="6"/>
+        <v>3000000</v>
+      </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
@@ -1546,13 +2091,34 @@
       <c r="C6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
+      <c r="D6" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Keuangan</v>
+      </c>
+      <c r="E6" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="F6" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Menikah</v>
+      </c>
+      <c r="G6" s="14">
+        <f t="shared" si="3"/>
+        <v>2000000</v>
+      </c>
+      <c r="H6" s="14">
+        <f t="shared" si="4"/>
+        <v>600000</v>
+      </c>
+      <c r="I6" s="14">
+        <f t="shared" si="5"/>
+        <v>500000</v>
+      </c>
+      <c r="J6" s="14">
+        <f t="shared" si="6"/>
+        <v>3100000</v>
+      </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
@@ -1561,13 +2127,34 @@
       <c r="C7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
+      <c r="D7" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Keuangan</v>
+      </c>
+      <c r="E7" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="F7" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Belum</v>
+      </c>
+      <c r="G7" s="14">
+        <f t="shared" si="3"/>
+        <v>2000000</v>
+      </c>
+      <c r="H7" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="14">
+        <f t="shared" si="5"/>
+        <v>500000</v>
+      </c>
+      <c r="J7" s="14">
+        <f t="shared" si="6"/>
+        <v>2500000</v>
+      </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
@@ -1576,13 +2163,34 @@
       <c r="C8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
+      <c r="D8" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Sekretaris</v>
+      </c>
+      <c r="E8" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="F8" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Menikah</v>
+      </c>
+      <c r="G8" s="14">
+        <f t="shared" si="3"/>
+        <v>3000000</v>
+      </c>
+      <c r="H8" s="14">
+        <f t="shared" si="4"/>
+        <v>900000</v>
+      </c>
+      <c r="I8" s="14">
+        <f t="shared" si="5"/>
+        <v>500000</v>
+      </c>
+      <c r="J8" s="14">
+        <f t="shared" si="6"/>
+        <v>4400000</v>
+      </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
@@ -1591,13 +2199,34 @@
       <c r="C9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
+      <c r="D9" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Manager</v>
+      </c>
+      <c r="E9" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F9" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Menikah</v>
+      </c>
+      <c r="G9" s="14">
+        <f t="shared" si="3"/>
+        <v>4000000</v>
+      </c>
+      <c r="H9" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="14">
+        <f t="shared" si="6"/>
+        <v>4000000</v>
+      </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -1606,13 +2235,34 @@
       <c r="C10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
+      <c r="D10" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Keuangan</v>
+      </c>
+      <c r="E10" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F10" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Belum</v>
+      </c>
+      <c r="G10" s="14">
+        <f t="shared" si="3"/>
+        <v>5000000</v>
+      </c>
+      <c r="H10" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="14">
+        <f t="shared" si="5"/>
+        <v>500000</v>
+      </c>
+      <c r="J10" s="14">
+        <f t="shared" si="6"/>
+        <v>5500000</v>
+      </c>
     </row>
     <row r="11" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
@@ -1621,27 +2271,27 @@
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="11" t="s">
@@ -1649,17 +2299,17 @@
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="19"/>
+      <c r="C18" s="22"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="11" t="s">
@@ -1667,12 +2317,12 @@
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="11" t="s">
@@ -1680,14 +2330,14 @@
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="11" t="s">
@@ -1695,14 +2345,14 @@
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="11"/>
@@ -1738,7 +2388,7 @@
     <mergeCell ref="B20:E20"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D1" r:id="rId1" xr:uid="{627ABB89-776A-47AA-81B2-9357D56C07B3}"/>
+    <hyperlink ref="D1" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/exercise/Admin/Admin Kantor/Tes Excel Admin Kantor.xlsx
+++ b/exercise/Admin/Admin Kantor/Tes Excel Admin Kantor.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Kantor\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CB98AA-5413-4C79-9581-5E39A613E1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Absolute" sheetId="2" r:id="rId1"/>
@@ -17,17 +18,48 @@
     <sheet name="3. F. Statistik" sheetId="4" r:id="rId3"/>
     <sheet name="4. IF" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="75">
   <si>
     <t>NIP</t>
   </si>
@@ -267,17 +299,53 @@
   <si>
     <t>Video Pembahasan</t>
   </si>
+  <si>
+    <r>
+      <t>$A2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → mengunci kolom A (baris pengali)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B$1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → mengunci baris 1 (kolom pengali)</t>
+    </r>
+  </si>
+  <si>
+    <t>Ctrl + D</t>
+  </si>
+  <si>
+    <t>Ctrl + R</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -363,6 +431,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="5">
@@ -467,7 +540,7 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -501,9 +574,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -534,8 +604,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -824,51 +900,51 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="12" width="5.7109375" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="15" t="s">
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="B2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+    </row>
+    <row r="3" spans="1:14">
       <c r="B3" s="4" t="s">
         <v>61</v>
       </c>
@@ -902,17 +978,20 @@
       <c r="L3" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N3" s="23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" s="12">
-        <f>C$3*$B4</f>
+        <f>$B4*C$3</f>
         <v>1</v>
       </c>
       <c r="D4" s="12">
-        <f t="shared" ref="D4:L13" si="0">D$3*$B4</f>
+        <f t="shared" ref="D4:L4" si="0">$B4*D$3</f>
         <v>2</v>
       </c>
       <c r="E4" s="12">
@@ -947,53 +1026,57 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N4" s="24"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="B5" s="2">
         <v>2</v>
       </c>
       <c r="C5" s="12">
-        <f t="shared" ref="C5:C13" si="1">C$3*$B5</f>
+        <f t="shared" ref="C5:L13" si="1">$B5*C$3</f>
         <v>2</v>
       </c>
       <c r="D5" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="E5" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="F5" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="G5" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="H5" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I5" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="J5" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="K5" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N5" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="B6" s="2">
         <v>3</v>
       </c>
@@ -1002,43 +1085,43 @@
         <v>3</v>
       </c>
       <c r="D6" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="E6" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="F6" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="G6" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="H6" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="I6" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="J6" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="K6" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14">
       <c r="B7" s="2">
         <v>4</v>
       </c>
@@ -1047,43 +1130,46 @@
         <v>4</v>
       </c>
       <c r="D7" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="E7" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="F7" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="G7" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="H7" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="I7" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="J7" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="K7" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N7" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="B8" s="2">
         <v>5</v>
       </c>
@@ -1092,43 +1178,46 @@
         <v>5</v>
       </c>
       <c r="D8" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="E8" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="F8" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="G8" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="H8" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="I8" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="J8" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="K8" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N8" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="B9" s="2">
         <v>6</v>
       </c>
@@ -1137,43 +1226,43 @@
         <v>6</v>
       </c>
       <c r="D9" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E9" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="F9" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="G9" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="H9" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="I9" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="J9" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="K9" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14">
       <c r="B10" s="2">
         <v>7</v>
       </c>
@@ -1182,43 +1271,43 @@
         <v>7</v>
       </c>
       <c r="D10" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="E10" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="F10" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="G10" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="H10" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="I10" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="J10" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="K10" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14">
       <c r="B11" s="2">
         <v>8</v>
       </c>
@@ -1227,43 +1316,43 @@
         <v>8</v>
       </c>
       <c r="D11" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E11" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="F11" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="G11" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="H11" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="I11" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="J11" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="K11" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14">
       <c r="B12" s="2">
         <v>9</v>
       </c>
@@ -1272,43 +1361,43 @@
         <v>9</v>
       </c>
       <c r="D12" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="E12" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="F12" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="G12" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="H12" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="I12" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
       <c r="J12" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="K12" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>81</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14">
       <c r="B13" s="2">
         <v>10</v>
       </c>
@@ -1317,43 +1406,43 @@
         <v>10</v>
       </c>
       <c r="D13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="E13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="F13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="G13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="H13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="I13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
       <c r="J13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="K13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -1372,7 +1461,7 @@
     <mergeCell ref="C1:L1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C1" r:id="rId1"/>
+    <hyperlink ref="C1" r:id="rId1" xr:uid="{1D8F91B2-4516-405D-81FD-321D8B0C5FF1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -1380,31 +1469,31 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="B1:H13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="8" width="9.7109375" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B2" s="15" t="s">
+    <row r="1" spans="2:8" ht="7.5" customHeight="1"/>
+    <row r="2" spans="2:8">
+      <c r="B2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-    </row>
-    <row r="3" spans="2:8" s="6" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+    </row>
+    <row r="3" spans="2:8" s="6" customFormat="1" ht="17.25">
       <c r="B3" s="7" t="s">
         <v>27</v>
       </c>
@@ -1427,7 +1516,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8">
       <c r="B4" s="2">
         <v>10</v>
       </c>
@@ -1443,19 +1532,19 @@
         <v>0.4</v>
       </c>
       <c r="F4" s="9">
-        <f>POWER(B4,3)</f>
+        <f>B4^3</f>
         <v>1000</v>
       </c>
       <c r="G4" s="9">
-        <f>POWER(C4,2)</f>
-        <v>16</v>
+        <f>SQRT(C4)</f>
+        <v>2</v>
       </c>
       <c r="H4" s="9">
-        <f>POWER((B4+C4),2)</f>
+        <f>(B4+C4)^2</f>
         <v>196</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8">
       <c r="B5" s="2">
         <v>9</v>
       </c>
@@ -1471,19 +1560,19 @@
         <v>1</v>
       </c>
       <c r="F5" s="9">
-        <f t="shared" ref="F5:F13" si="2">POWER(B5,3)</f>
+        <f t="shared" ref="F5:F13" si="2">B5^3</f>
         <v>729</v>
       </c>
       <c r="G5" s="9">
-        <f t="shared" ref="G5:G13" si="3">POWER(C5,2)</f>
-        <v>81</v>
+        <f t="shared" ref="G5:G13" si="3">SQRT(C5)</f>
+        <v>3</v>
       </c>
       <c r="H5" s="9">
-        <f t="shared" ref="H5:H13" si="4">POWER((B5+C5),2)</f>
+        <f t="shared" ref="H5:H13" si="4">(B5+C5)^2</f>
         <v>324</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8">
       <c r="B6" s="2">
         <v>8</v>
       </c>
@@ -1504,14 +1593,14 @@
       </c>
       <c r="G6" s="9">
         <f t="shared" si="3"/>
-        <v>256</v>
+        <v>4</v>
       </c>
       <c r="H6" s="9">
         <f t="shared" si="4"/>
         <v>576</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8">
       <c r="B7" s="2">
         <v>7</v>
       </c>
@@ -1532,14 +1621,14 @@
       </c>
       <c r="G7" s="9">
         <f t="shared" si="3"/>
-        <v>625</v>
+        <v>5</v>
       </c>
       <c r="H7" s="9">
         <f t="shared" si="4"/>
         <v>1024</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8">
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -1560,14 +1649,14 @@
       </c>
       <c r="G8" s="9">
         <f t="shared" si="3"/>
-        <v>1296</v>
+        <v>6</v>
       </c>
       <c r="H8" s="9">
         <f t="shared" si="4"/>
         <v>1764</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -1588,14 +1677,14 @@
       </c>
       <c r="G9" s="9">
         <f t="shared" si="3"/>
-        <v>2401</v>
+        <v>7</v>
       </c>
       <c r="H9" s="9">
         <f t="shared" si="4"/>
         <v>2916</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8">
       <c r="B10" s="2">
         <v>4</v>
       </c>
@@ -1616,14 +1705,14 @@
       </c>
       <c r="G10" s="9">
         <f t="shared" si="3"/>
-        <v>4096</v>
+        <v>8</v>
       </c>
       <c r="H10" s="9">
         <f t="shared" si="4"/>
         <v>4624</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8">
       <c r="B11" s="2">
         <v>3</v>
       </c>
@@ -1644,14 +1733,14 @@
       </c>
       <c r="G11" s="9">
         <f t="shared" si="3"/>
-        <v>6561</v>
+        <v>9</v>
       </c>
       <c r="H11" s="9">
         <f t="shared" si="4"/>
         <v>7056</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8">
       <c r="B12" s="2">
         <v>2</v>
       </c>
@@ -1672,14 +1761,14 @@
       </c>
       <c r="G12" s="9">
         <f t="shared" si="3"/>
-        <v>10000</v>
+        <v>10</v>
       </c>
       <c r="H12" s="9">
         <f t="shared" si="4"/>
         <v>10404</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8">
       <c r="B13" s="2">
         <v>1</v>
       </c>
@@ -1700,7 +1789,7 @@
       </c>
       <c r="G13" s="9">
         <f t="shared" si="3"/>
-        <v>14641</v>
+        <v>11</v>
       </c>
       <c r="H13" s="9">
         <f t="shared" si="4"/>
@@ -1716,12 +1805,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="B1:F14"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
@@ -1732,17 +1821,17 @@
     <col min="7" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="15" t="s">
+    <row r="1" spans="2:6" ht="6.75" customHeight="1"/>
+    <row r="2" spans="2:6">
+      <c r="B2" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-    </row>
-    <row r="3" spans="2:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+    </row>
+    <row r="3" spans="2:6" s="6" customFormat="1">
       <c r="B3" s="5" t="s">
         <v>33</v>
       </c>
@@ -1759,7 +1848,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6">
       <c r="B4" s="2" t="s">
         <v>34</v>
       </c>
@@ -1772,12 +1861,12 @@
       <c r="E4" s="8">
         <v>2000</v>
       </c>
-      <c r="F4" s="13">
-        <f>E4*E4</f>
-        <v>4000000</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F4" s="25">
+        <f>E4*D4</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6">
       <c r="B5" s="2" t="s">
         <v>35</v>
       </c>
@@ -1790,12 +1879,12 @@
       <c r="E5" s="8">
         <v>3000</v>
       </c>
-      <c r="F5" s="13">
-        <f t="shared" ref="F5:F8" si="0">E5*E5</f>
-        <v>9000000</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F5" s="25">
+        <f t="shared" ref="F5:F8" si="0">E5*D5</f>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
       <c r="B6" s="2" t="s">
         <v>36</v>
       </c>
@@ -1808,12 +1897,12 @@
       <c r="E6" s="8">
         <v>4000</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="25">
         <f t="shared" si="0"/>
-        <v>16000000</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
       <c r="B7" s="2" t="s">
         <v>37</v>
       </c>
@@ -1826,12 +1915,12 @@
       <c r="E7" s="8">
         <v>5000</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="25">
         <f t="shared" si="0"/>
-        <v>25000000</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6">
       <c r="B8" s="2" t="s">
         <v>38</v>
       </c>
@@ -1844,69 +1933,69 @@
       <c r="E8" s="8">
         <v>6000</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="25">
         <f t="shared" si="0"/>
-        <v>36000000</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="17" t="s">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="13">
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="25">
         <f>SUM(F4:F8)</f>
-        <v>90000000</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="17" t="s">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="13">
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="25">
         <f>MAX(F4:F8)</f>
-        <v>36000000</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="17" t="s">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="13">
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="25">
         <f>MIN(F4:F8)</f>
-        <v>4000000</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="17" t="s">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="13">
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="25">
         <f>AVERAGE(F4:F8)</f>
-        <v>18000000</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="17" t="s">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="19"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18"/>
       <c r="F14" s="12">
-        <f>SUM(D4:D8)</f>
-        <v>15</v>
+        <f>COUNT(D4:D8)</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1923,12 +2012,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="B1:J31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="3.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" style="1" customWidth="1"/>
@@ -1937,17 +2026,17 @@
     <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10">
       <c r="B1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-    </row>
-    <row r="2" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+    </row>
+    <row r="2" spans="2:10" s="6" customFormat="1">
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1976,403 +2065,403 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="12" t="str">
-        <f>IF(LEFT(B3,3)="MAN","Manager",IF(LEFT(B3,3)="SKT","Sekretaris",IF(LEFT(B3,3)="KEU","Keuangan")))</f>
+      <c r="D3" s="12" t="str" cm="1">
+        <f t="array" ref="D3">_xlfn.IFS(LEFT(B3,3)="MAN","Manager",LEFT(B3,3)="SKT","Sekretaris",LEFT(B3,3)="KEU","Keuangan")</f>
         <v>Manager</v>
       </c>
       <c r="E3" s="12" t="str">
         <f>MID(B3,5,1)</f>
         <v>1</v>
       </c>
-      <c r="F3" s="12" t="str">
-        <f>IF(RIGHT(B3,1)="A","Menikah","Belum")</f>
+      <c r="F3" s="12" t="str" cm="1">
+        <f t="array" ref="F3">_xlfn.IFS(RIGHT(B3,1)="A","Menikah",RIGHT(B3,1)="B","Belum")</f>
         <v>Menikah</v>
       </c>
-      <c r="G3" s="14">
-        <f>IF(E3="1",5000000,IF(E3="2",4000000,IF(E3="3",3000000,IF(E3="4",2000000))))</f>
+      <c r="G3" s="13" cm="1">
+        <f t="array" ref="G3">_xlfn.IFS(VALUE(E3)=1,5000000,VALUE(E3)=2,4000000,VALUE(E3)=3,3000000,VALUE(E3)=4,2000000)</f>
         <v>5000000</v>
       </c>
-      <c r="H3" s="14">
-        <f>IF(AND(OR(E3="3",E3="4"),F3="Menikah"),G3*0.3,0)</f>
+      <c r="H3" s="13">
+        <f>IF(AND(OR(VALUE(E3)=3,VALUE(E3)=4),F3="Menikah"),30%*G3,0)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <f>IF(OR(D3="Sekretaris",D3="Keuangan"),500000,0)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="13">
         <f>G3+H3+I3</f>
         <v>5000000</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="12" t="str">
-        <f t="shared" ref="D4:D10" si="0">IF(LEFT(B4,3)="MAN","Manager",IF(LEFT(B4,3)="SKT","Sekretaris",IF(LEFT(B4,3)="KEU","Keuangan")))</f>
+      <c r="D4" s="12" t="str" cm="1">
+        <f t="array" ref="D4">_xlfn.IFS(LEFT(B4,3)="MAN","Manager",LEFT(B4,3)="SKT","Sekretaris",LEFT(B4,3)="KEU","Keuangan")</f>
         <v>Sekretaris</v>
       </c>
       <c r="E4" s="12" t="str">
-        <f t="shared" ref="E4:E10" si="1">MID(B4,5,1)</f>
+        <f t="shared" ref="E4:E10" si="0">MID(B4,5,1)</f>
         <v>2</v>
       </c>
-      <c r="F4" s="12" t="str">
-        <f t="shared" ref="F4:F10" si="2">IF(RIGHT(B4,1)="A","Menikah","Belum")</f>
+      <c r="F4" s="12" t="str" cm="1">
+        <f t="array" ref="F4">_xlfn.IFS(RIGHT(B4,1)="A","Menikah",RIGHT(B4,1)="B","Belum")</f>
         <v>Belum</v>
       </c>
-      <c r="G4" s="14">
-        <f t="shared" ref="G4:G10" si="3">IF(E4="1",5000000,IF(E4="2",4000000,IF(E4="3",3000000,IF(E4="4",2000000))))</f>
+      <c r="G4" s="13" cm="1">
+        <f t="array" ref="G4">_xlfn.IFS(VALUE(E4)=1,5000000,VALUE(E4)=2,4000000,VALUE(E4)=3,3000000,VALUE(E4)=4,2000000)</f>
         <v>4000000</v>
       </c>
-      <c r="H4" s="14">
-        <f t="shared" ref="H4:H10" si="4">IF(AND(OR(E4="3",E4="4"),F4="Menikah"),G4*0.3,0)</f>
+      <c r="H4" s="13">
+        <f t="shared" ref="H4:H10" si="1">IF(AND(OR(VALUE(E4)=3,VALUE(E4)=4),F4="Menikah"),30%*G4,0)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="14">
-        <f t="shared" ref="I4:I10" si="5">IF(OR(D4="Sekretaris",D4="Keuangan"),500000,0)</f>
+      <c r="I4" s="13">
+        <f t="shared" ref="I4:I10" si="2">IF(OR(D4="Sekretaris",D4="Keuangan"),500000,0)</f>
         <v>500000</v>
       </c>
-      <c r="J4" s="14">
-        <f t="shared" ref="J4:J10" si="6">G4+H4+I4</f>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J10" si="3">G4+H4+I4</f>
         <v>4500000</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10">
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="12" t="str">
+      <c r="D5" s="12" t="str" cm="1">
+        <f t="array" ref="D5">_xlfn.IFS(LEFT(B5,3)="MAN","Manager",LEFT(B5,3)="SKT","Sekretaris",LEFT(B5,3)="KEU","Keuangan")</f>
+        <v>Manager</v>
+      </c>
+      <c r="E5" s="12" t="str">
         <f t="shared" si="0"/>
-        <v>Manager</v>
-      </c>
-      <c r="E5" s="12" t="str">
-        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F5" s="12" t="str">
+      <c r="F5" s="12" t="str" cm="1">
+        <f t="array" ref="F5">_xlfn.IFS(RIGHT(B5,1)="A","Menikah",RIGHT(B5,1)="B","Belum")</f>
+        <v>Belum</v>
+      </c>
+      <c r="G5" s="13" cm="1">
+        <f t="array" ref="G5">_xlfn.IFS(VALUE(E5)=1,5000000,VALUE(E5)=2,4000000,VALUE(E5)=3,3000000,VALUE(E5)=4,2000000)</f>
+        <v>3000000</v>
+      </c>
+      <c r="H5" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="13">
         <f t="shared" si="2"/>
-        <v>Belum</v>
-      </c>
-      <c r="G5" s="14">
+        <v>0</v>
+      </c>
+      <c r="J5" s="13">
         <f t="shared" si="3"/>
         <v>3000000</v>
       </c>
-      <c r="H5" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I5" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J5" s="14">
-        <f t="shared" si="6"/>
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="2:10">
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="12" t="str">
+      <c r="D6" s="12" t="str" cm="1">
+        <f t="array" ref="D6">_xlfn.IFS(LEFT(B6,3)="MAN","Manager",LEFT(B6,3)="SKT","Sekretaris",LEFT(B6,3)="KEU","Keuangan")</f>
+        <v>Keuangan</v>
+      </c>
+      <c r="E6" s="12" t="str">
         <f t="shared" si="0"/>
-        <v>Keuangan</v>
-      </c>
-      <c r="E6" s="12" t="str">
-        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F6" s="12" t="str">
+      <c r="F6" s="12" t="str" cm="1">
+        <f t="array" ref="F6">_xlfn.IFS(RIGHT(B6,1)="A","Menikah",RIGHT(B6,1)="B","Belum")</f>
+        <v>Menikah</v>
+      </c>
+      <c r="G6" s="13" cm="1">
+        <f t="array" ref="G6">_xlfn.IFS(VALUE(E6)=1,5000000,VALUE(E6)=2,4000000,VALUE(E6)=3,3000000,VALUE(E6)=4,2000000)</f>
+        <v>2000000</v>
+      </c>
+      <c r="H6" s="13">
+        <f t="shared" si="1"/>
+        <v>600000</v>
+      </c>
+      <c r="I6" s="13">
         <f t="shared" si="2"/>
-        <v>Menikah</v>
-      </c>
-      <c r="G6" s="14">
+        <v>500000</v>
+      </c>
+      <c r="J6" s="13">
         <f t="shared" si="3"/>
-        <v>2000000</v>
-      </c>
-      <c r="H6" s="14">
-        <f t="shared" si="4"/>
-        <v>600000</v>
-      </c>
-      <c r="I6" s="14">
-        <f t="shared" si="5"/>
-        <v>500000</v>
-      </c>
-      <c r="J6" s="14">
-        <f t="shared" si="6"/>
         <v>3100000</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10">
       <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="12" t="str">
+      <c r="D7" s="12" t="str" cm="1">
+        <f t="array" ref="D7">_xlfn.IFS(LEFT(B7,3)="MAN","Manager",LEFT(B7,3)="SKT","Sekretaris",LEFT(B7,3)="KEU","Keuangan")</f>
+        <v>Keuangan</v>
+      </c>
+      <c r="E7" s="12" t="str">
         <f t="shared" si="0"/>
-        <v>Keuangan</v>
-      </c>
-      <c r="E7" s="12" t="str">
-        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F7" s="12" t="str">
+      <c r="F7" s="12" t="str" cm="1">
+        <f t="array" ref="F7">_xlfn.IFS(RIGHT(B7,1)="A","Menikah",RIGHT(B7,1)="B","Belum")</f>
+        <v>Belum</v>
+      </c>
+      <c r="G7" s="13" cm="1">
+        <f t="array" ref="G7">_xlfn.IFS(VALUE(E7)=1,5000000,VALUE(E7)=2,4000000,VALUE(E7)=3,3000000,VALUE(E7)=4,2000000)</f>
+        <v>2000000</v>
+      </c>
+      <c r="H7" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="13">
         <f t="shared" si="2"/>
-        <v>Belum</v>
-      </c>
-      <c r="G7" s="14">
+        <v>500000</v>
+      </c>
+      <c r="J7" s="13">
         <f t="shared" si="3"/>
-        <v>2000000</v>
-      </c>
-      <c r="H7" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="14">
-        <f t="shared" si="5"/>
-        <v>500000</v>
-      </c>
-      <c r="J7" s="14">
-        <f t="shared" si="6"/>
         <v>2500000</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10">
       <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="12" t="str">
+      <c r="D8" s="12" t="str" cm="1">
+        <f t="array" ref="D8">_xlfn.IFS(LEFT(B8,3)="MAN","Manager",LEFT(B8,3)="SKT","Sekretaris",LEFT(B8,3)="KEU","Keuangan")</f>
+        <v>Sekretaris</v>
+      </c>
+      <c r="E8" s="12" t="str">
         <f t="shared" si="0"/>
-        <v>Sekretaris</v>
-      </c>
-      <c r="E8" s="12" t="str">
-        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F8" s="12" t="str">
+      <c r="F8" s="12" t="str" cm="1">
+        <f t="array" ref="F8">_xlfn.IFS(RIGHT(B8,1)="A","Menikah",RIGHT(B8,1)="B","Belum")</f>
+        <v>Menikah</v>
+      </c>
+      <c r="G8" s="13" cm="1">
+        <f t="array" ref="G8">_xlfn.IFS(VALUE(E8)=1,5000000,VALUE(E8)=2,4000000,VALUE(E8)=3,3000000,VALUE(E8)=4,2000000)</f>
+        <v>3000000</v>
+      </c>
+      <c r="H8" s="13">
+        <f t="shared" si="1"/>
+        <v>900000</v>
+      </c>
+      <c r="I8" s="13">
         <f t="shared" si="2"/>
-        <v>Menikah</v>
-      </c>
-      <c r="G8" s="14">
+        <v>500000</v>
+      </c>
+      <c r="J8" s="13">
         <f t="shared" si="3"/>
-        <v>3000000</v>
-      </c>
-      <c r="H8" s="14">
-        <f t="shared" si="4"/>
-        <v>900000</v>
-      </c>
-      <c r="I8" s="14">
-        <f t="shared" si="5"/>
-        <v>500000</v>
-      </c>
-      <c r="J8" s="14">
-        <f t="shared" si="6"/>
         <v>4400000</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10">
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="12" t="str">
+      <c r="D9" s="12" t="str" cm="1">
+        <f t="array" ref="D9">_xlfn.IFS(LEFT(B9,3)="MAN","Manager",LEFT(B9,3)="SKT","Sekretaris",LEFT(B9,3)="KEU","Keuangan")</f>
+        <v>Manager</v>
+      </c>
+      <c r="E9" s="12" t="str">
         <f t="shared" si="0"/>
-        <v>Manager</v>
-      </c>
-      <c r="E9" s="12" t="str">
-        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F9" s="12" t="str">
+      <c r="F9" s="12" t="str" cm="1">
+        <f t="array" ref="F9">_xlfn.IFS(RIGHT(B9,1)="A","Menikah",RIGHT(B9,1)="B","Belum")</f>
+        <v>Menikah</v>
+      </c>
+      <c r="G9" s="13" cm="1">
+        <f t="array" ref="G9">_xlfn.IFS(VALUE(E9)=1,5000000,VALUE(E9)=2,4000000,VALUE(E9)=3,3000000,VALUE(E9)=4,2000000)</f>
+        <v>4000000</v>
+      </c>
+      <c r="H9" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="13">
         <f t="shared" si="2"/>
-        <v>Menikah</v>
-      </c>
-      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13">
         <f t="shared" si="3"/>
         <v>4000000</v>
       </c>
-      <c r="H9" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="14">
-        <f t="shared" si="6"/>
-        <v>4000000</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="2:10">
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="12" t="str">
+      <c r="D10" s="12" t="str" cm="1">
+        <f t="array" ref="D10">_xlfn.IFS(LEFT(B10,3)="MAN","Manager",LEFT(B10,3)="SKT","Sekretaris",LEFT(B10,3)="KEU","Keuangan")</f>
+        <v>Keuangan</v>
+      </c>
+      <c r="E10" s="12" t="str">
         <f t="shared" si="0"/>
-        <v>Keuangan</v>
-      </c>
-      <c r="E10" s="12" t="str">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F10" s="12" t="str">
+      <c r="F10" s="12" t="str" cm="1">
+        <f t="array" ref="F10">_xlfn.IFS(RIGHT(B10,1)="A","Menikah",RIGHT(B10,1)="B","Belum")</f>
+        <v>Belum</v>
+      </c>
+      <c r="G10" s="13" cm="1">
+        <f t="array" ref="G10">_xlfn.IFS(VALUE(E10)=1,5000000,VALUE(E10)=2,4000000,VALUE(E10)=3,3000000,VALUE(E10)=4,2000000)</f>
+        <v>5000000</v>
+      </c>
+      <c r="H10" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="13">
         <f t="shared" si="2"/>
-        <v>Belum</v>
-      </c>
-      <c r="G10" s="14">
+        <v>500000</v>
+      </c>
+      <c r="J10" s="13">
         <f t="shared" si="3"/>
-        <v>5000000</v>
-      </c>
-      <c r="H10" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="14">
-        <f t="shared" si="5"/>
-        <v>500000</v>
-      </c>
-      <c r="J10" s="14">
-        <f t="shared" si="6"/>
         <v>5500000</v>
       </c>
     </row>
-    <row r="11" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" ht="9" customHeight="1"/>
+    <row r="12" spans="2:10">
       <c r="B12" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="22" t="s">
+    <row r="13" spans="2:10">
+      <c r="B13" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="23" t="s">
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="B14" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="22" t="s">
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="B15" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+    </row>
+    <row r="16" spans="2:10">
       <c r="B16" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="22" t="s">
+    <row r="17" spans="2:7">
+      <c r="B17" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="22" t="s">
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="22"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C18" s="21"/>
+    </row>
+    <row r="19" spans="2:7">
       <c r="B19" s="11" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="22" t="s">
+    <row r="20" spans="2:7">
+      <c r="B20" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+    </row>
+    <row r="21" spans="2:7">
       <c r="B21" s="11" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="22" t="s">
+    <row r="22" spans="2:7">
+      <c r="B22" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+    </row>
+    <row r="23" spans="2:7">
       <c r="B23" s="11" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="22" t="s">
+    <row r="24" spans="2:7">
+      <c r="B24" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+    </row>
+    <row r="25" spans="2:7">
       <c r="B25" s="11"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7">
       <c r="B26" s="11"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7">
       <c r="B27" s="11"/>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7">
       <c r="B28" s="11"/>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7">
       <c r="B29" s="11"/>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7">
       <c r="B30" s="11"/>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7">
       <c r="B31" s="11"/>
     </row>
   </sheetData>
@@ -2388,7 +2477,7 @@
     <mergeCell ref="B20:E20"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D1" r:id="rId1"/>
+    <hyperlink ref="D1" r:id="rId1" xr:uid="{627ABB89-776A-47AA-81B2-9357D56C07B3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
